--- a/artfynd/A 63531-2025 artfynd.xlsx
+++ b/artfynd/A 63531-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>89825469</v>
+        <v>89825476</v>
       </c>
       <c r="B2" t="n">
-        <v>95220</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>2609</v>
+        <v>349</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Blåsfliksmossa</t>
+          <t>Späd hårgräsmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lejeunea cavifolia</t>
+          <t>Brachythecium tommasinii</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ehrh.) Lindb.</t>
+          <t>(Sendtn. ex Boulay) Ignatov &amp; Huttunen</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496697.108629337</v>
+        <v>496687</v>
       </c>
       <c r="R2" t="n">
-        <v>6594157.198087126</v>
+        <v>6594148</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2020-11-10</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2020-11-10</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -779,7 +764,7 @@
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>Kalklodyta i bäckkanten</t>
+          <t>Kalksten i kalkbrott</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr"/>
@@ -801,15 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>89825465</v>
+        <v>62689560</v>
       </c>
       <c r="B3" t="n">
-        <v>92895</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>95944</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -817,37 +797,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2676</v>
+        <v>2362</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Grov baronmossa</t>
+          <t>Blek stjärnmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Anomodon viticulosus</t>
+          <t>Mnium stellare</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Hook. &amp; Taylor</t>
+          <t>Hedw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Knapptorpsbäcken, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496697.108629337</v>
+        <v>496692</v>
       </c>
       <c r="R3" t="n">
-        <v>6594157.198087126</v>
+        <v>6594147</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -871,22 +851,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2020-11-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -900,18 +870,23 @@
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Henrik Weibull</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -922,15 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>88402982</v>
+        <v>89825469</v>
       </c>
       <c r="B4" t="n">
-        <v>90319</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97796</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,37 +908,37 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4769</v>
+        <v>2609</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Svavelriska</t>
+          <t>Blåsfliksmossa</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Lactarius scrobiculatus</t>
+          <t>Lejeunea cavifolia</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Scop.:Fr.) Fr.</t>
+          <t>(Ehrh.) Lindb.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>496671.166785097</v>
+        <v>496697</v>
       </c>
       <c r="R4" t="n">
-        <v>6594165.855740821</v>
+        <v>6594157</v>
       </c>
       <c r="S4" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -992,22 +962,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1021,18 +981,23 @@
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>blandskog i bäckdal</t>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Kalklodyta i bäckkanten</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1043,15 +1008,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>88402981</v>
+        <v>62689568</v>
       </c>
       <c r="B5" t="n">
-        <v>101680</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1059,34 +1019,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>222412</v>
+        <v>2666</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496702.1994296426</v>
+        <v>496693</v>
       </c>
       <c r="R5" t="n">
-        <v>6594160.24121223</v>
+        <v>6594148</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1113,22 +1073,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,18 +1092,23 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>blockig blandskog på kalk</t>
+          <t>Klippa</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1164,15 +1119,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>88403102</v>
+        <v>62689569</v>
       </c>
       <c r="B6" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1180,34 +1130,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>222498</v>
+        <v>2666</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>Schreb.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496671.166785097</v>
+        <v>496708</v>
       </c>
       <c r="R6" t="n">
-        <v>6594165.855740821</v>
+        <v>6594183</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1234,22 +1184,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-28</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1263,18 +1203,23 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>blandskog i bäckdal</t>
+          <t>Bäckdal</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>Kalkhaltig klippa</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Tommy Pettersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1285,15 +1230,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>88403132</v>
+        <v>89342445</v>
       </c>
       <c r="B7" t="n">
-        <v>93145</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1301,34 +1241,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2667</v>
+        <v>2666</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Platt fjädermossa</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Neckera complanata</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Hedw.) Huebener</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496702.1994296426</v>
+        <v>496708</v>
       </c>
       <c r="R7" t="n">
-        <v>6594160.24121223</v>
+        <v>6594184</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1355,22 +1295,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-10-25</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1384,18 +1314,23 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>block med kalkinslag</t>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>lodyta</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Jenny Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1406,53 +1341,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>88403119</v>
+        <v>89825479</v>
       </c>
       <c r="B8" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96439</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220785</v>
+        <v>2666</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Grov fjädermossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Exsertotheca crispa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorpsbäcken, Vstm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496702.1994296426</v>
+        <v>496687</v>
       </c>
       <c r="R8" t="n">
-        <v>6594160.24121223</v>
+        <v>6594148</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1476,22 +1406,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2020-11-10</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1505,18 +1425,23 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>blockig blandskog på kalk</t>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>Kalksten i kalkbrott</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Hans Rydberg</t>
+          <t>Henrik Weibull</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1527,15 +1452,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>88403140</v>
+        <v>62689565</v>
       </c>
       <c r="B9" t="n">
-        <v>85077</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>96437</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1543,34 +1463,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3762</v>
+        <v>2667</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Platt fjädermossa</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Alleniella complanata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Knapptorpsskogen, Vstm</t>
+          <t>Knapptorp, Vstm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496702.1994296426</v>
+        <v>496702</v>
       </c>
       <c r="R9" t="n">
-        <v>6594160.24121223</v>
+        <v>6594149</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1597,22 +1517,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2020-10-06</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2016-10-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1626,21 +1536,2523 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>blockig blandskog på kalk</t>
+          <t>Blandskog</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>Klippa</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>88403132</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>496702</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6594160</v>
+      </c>
+      <c r="S10" t="n">
+        <v>25</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>block med kalkinslag</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
+      <c r="AX10" t="inlineStr">
         <is>
           <t>Hans Rydberg</t>
         </is>
       </c>
-      <c r="AY9" t="inlineStr">
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>89342441</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>496708</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6594184</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>89825475</v>
+      </c>
+      <c r="B12" t="n">
+        <v>96437</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>2667</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Platt fjädermossa</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Alleniella complanata</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Hedw.) S.Olsson, Enroth &amp; D.Quandt</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>496687</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6594148</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2020-11-10</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2020-11-10</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>Kalksten i kalkbrott</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>62689552</v>
+      </c>
+      <c r="B13" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Knapptorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>496687</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6594222</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2016-10-28</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2016-10-28</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Bäckdal</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>Kalkhaltig klippa</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Henrik Josefsson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Tommy Pettersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>88403133</v>
+      </c>
+      <c r="B14" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>496700</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6594152</v>
+      </c>
+      <c r="S14" t="n">
+        <v>25</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>blockig blandskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>89342442</v>
+      </c>
+      <c r="B15" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>496708</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6594184</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>lodyta</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>89825478</v>
+      </c>
+      <c r="B16" t="n">
+        <v>96441</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>2668</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Trubbfjädermossa</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Homalia trichomanoides</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Hedw.) Brid.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>496687</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6594148</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2020-11-10</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2020-11-10</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>Kalksten i kalkbrott</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>89825465</v>
+      </c>
+      <c r="B17" t="n">
+        <v>96186</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>2676</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Grov baronmossa</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Anomodon viticulosus</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Hedw.) Hook. &amp; Taylor</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>496697</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6594157</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2020-11-10</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2020-11-10</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Barrskog med lövinslag intill bäck med kalkklippor</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Henrik Weibull</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>88403033</v>
+      </c>
+      <c r="B18" t="n">
+        <v>96338</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>2809</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Mörk husmossa</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Hylocomiastrum umbratum</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Hedw.) M.Fleisch.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>496708</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6594220</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>bäckdal med lövblandskog</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>89342465</v>
+      </c>
+      <c r="B19" t="n">
+        <v>96350</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>2813</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Skogshakmossa</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Rhytidiadelphus subpinnatus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Lindb.) T.J.Kop.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>496612</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6594316</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>89342459</v>
+      </c>
+      <c r="B20" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>496685</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6594247</v>
+      </c>
+      <c r="S20" t="n">
+        <v>25</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>88403140</v>
+      </c>
+      <c r="B21" t="n">
+        <v>87146</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>496702</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6594160</v>
+      </c>
+      <c r="S21" t="n">
+        <v>25</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>blockig blandskog på kalk</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>88402982</v>
+      </c>
+      <c r="B22" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>496671</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6594166</v>
+      </c>
+      <c r="S22" t="n">
+        <v>25</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>blandskog i bäckdal</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>88402983</v>
+      </c>
+      <c r="B23" t="n">
+        <v>92869</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>4769</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svavelriska</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Lactarius scrobiculatus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Scop.) Fr.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>496708</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6594220</v>
+      </c>
+      <c r="S23" t="n">
+        <v>25</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>bäckdal med lövblandskog</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>117866106</v>
+      </c>
+      <c r="B24" t="n">
+        <v>43285</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>201143</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Ängsblåvinge</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Cyaniris semiargus</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Rottemburg, 1775)</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Knapptorps Gård, järnvägen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>496598</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6594240</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-06-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>121698034</v>
+      </c>
+      <c r="B25" t="n">
+        <v>98186</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220250</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Strutbräken</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Matteuccia struthiopteris</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(L.) Tod.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>vinterståndare</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr"/>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken uppströms banvallen., Vstm</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>496681</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6594265</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2024-12-20</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>10:30</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF25" t="inlineStr"/>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Anders Carlberg</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>88403119</v>
+      </c>
+      <c r="B26" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>496702</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6594160</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>blockig blandskog på kalk</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>88403120</v>
+      </c>
+      <c r="B27" t="n">
+        <v>106813</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>496669</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6594261</v>
+      </c>
+      <c r="S27" t="n">
+        <v>25</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>lövrik blandskog</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>88402981</v>
+      </c>
+      <c r="B28" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>496702</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6594160</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>blockig blandskog på kalk</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>88403100</v>
+      </c>
+      <c r="B29" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>496700</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6594152</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>blockig blandskog</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>88403102</v>
+      </c>
+      <c r="B30" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>496671</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6594166</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>blandskog i bäckdal</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>89342463</v>
+      </c>
+      <c r="B31" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Knapptorpsbäcken, Vstm</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>496663</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6594270</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2020-10-25</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>kalkgranskog</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jenny Andersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>88402986</v>
+      </c>
+      <c r="B32" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Knapptorpsskogen, Vstm</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>496700</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6594152</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Nora</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Viker</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2020-10-06</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>blockig blandskog</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Hans Rydberg</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>

--- a/artfynd/A 63531-2025 artfynd.xlsx
+++ b/artfynd/A 63531-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825476</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689560</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825469</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689568</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1227,6 +1252,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689569</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1338,6 +1368,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342445</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1449,6 +1484,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825479</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1560,6 +1600,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689565</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1666,6 +1711,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403132</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1777,6 +1827,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342441</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1888,6 +1943,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825475</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1999,6 +2059,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/62689552</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2105,6 +2170,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403133</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2216,6 +2286,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342442</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2327,6 +2402,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825478</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2433,6 +2513,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89825465</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2537,6 +2622,11 @@
       <c r="AY18" t="inlineStr">
         <is>
           <t>Länsstyrelsen i Örebro län, inventering</t>
+        </is>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403033</t>
         </is>
       </c>
     </row>
@@ -2650,6 +2740,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342465</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2756,6 +2851,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342459</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2862,6 +2962,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403140</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2968,6 +3073,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402982</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3074,6 +3184,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402983</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3199,6 +3314,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/117866106</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3315,6 +3435,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121698034</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3421,6 +3546,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403119</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3527,6 +3657,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403120</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3633,6 +3768,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402981</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3739,6 +3879,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403100</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3845,6 +3990,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88403102</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3951,6 +4101,11 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89342463</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4057,8 +4212,46 @@
           <t>Länsstyrelsen i Örebro län, inventering</t>
         </is>
       </c>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/88402986</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>